--- a/ValueSet-ACCESSBHDiagnosisVS.xlsx
+++ b/ValueSet-ACCESSBHDiagnosisVS.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-26T23:16:42-05:00</t>
+    <t>2026-03-06T16:03:26-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-ACCESSBHDiagnosisVS.xlsx
+++ b/ValueSet-ACCESSBHDiagnosisVS.xlsx
@@ -24,13 +24,13 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://globalalliantinc.com/access/ValueSet/ACCESSBHDiagnosisVS</t>
+    <t>https://dsacms.github.io/cmmi-access-model/ValueSet/ACCESSBHDiagnosisVS</t>
   </si>
   <si>
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.9.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-06T16:03:26-05:00</t>
+    <t>2026-03-12T23:55:37-07:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-ACCESSBHDiagnosisVS.xlsx
+++ b/ValueSet-ACCESSBHDiagnosisVS.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.1</t>
+    <t>0.9.6</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-12T23:55:37-07:00</t>
+    <t>2026-04-24T13:45:33-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-ACCESSBHDiagnosisVS.xlsx
+++ b/ValueSet-ACCESSBHDiagnosisVS.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.6</t>
+    <t>0.9.8</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T13:45:33-04:00</t>
+    <t>2026-05-18T15:59:44-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-ACCESSBHDiagnosisVS.xlsx
+++ b/ValueSet-ACCESSBHDiagnosisVS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-18T15:59:44-04:00</t>
+    <t>2026-05-20T09:30:43-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-ACCESSBHDiagnosisVS.xlsx
+++ b/ValueSet-ACCESSBHDiagnosisVS.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="171">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.8</t>
+    <t>0.9.11</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-20T09:30:43-04:00</t>
+    <t>2026-06-04T22:54:52-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -105,16 +105,22 @@
     <t>Concept</t>
   </si>
   <si>
+    <t>F06.30</t>
+  </si>
+  <si>
+    <t>Mood disorder due to known physiological condition, unspecified</t>
+  </si>
+  <si>
     <t>F06.31</t>
   </si>
   <si>
     <t>Mood disorder due to known physiological condition with depressive features</t>
   </si>
   <si>
-    <t>F06.32</t>
-  </si>
-  <si>
-    <t>Mood disorder due to known physiological condition with major depressive-like episode</t>
+    <t>F06.4</t>
+  </si>
+  <si>
+    <t>Anxiety disorder due to known physiological condition</t>
   </si>
   <si>
     <t>F32.0</t>
@@ -243,6 +249,216 @@
     <t>Dysthymic disorder</t>
   </si>
   <si>
+    <t>F34.81</t>
+  </si>
+  <si>
+    <t>Disruptive mood dysregulation disorder</t>
+  </si>
+  <si>
+    <t>F34.89</t>
+  </si>
+  <si>
+    <t>Other specified persistent mood disorders</t>
+  </si>
+  <si>
+    <t>F34.9</t>
+  </si>
+  <si>
+    <t>Persistent mood [affective] disorder, unspecified</t>
+  </si>
+  <si>
+    <t>F40.00</t>
+  </si>
+  <si>
+    <t>Agoraphobia, unspecified</t>
+  </si>
+  <si>
+    <t>F40.01</t>
+  </si>
+  <si>
+    <t>Agoraphobia with panic disorder</t>
+  </si>
+  <si>
+    <t>F40.02</t>
+  </si>
+  <si>
+    <t>Agoraphobia without panic disorder</t>
+  </si>
+  <si>
+    <t>F40.10</t>
+  </si>
+  <si>
+    <t>Social phobia, unspecified</t>
+  </si>
+  <si>
+    <t>F40.11</t>
+  </si>
+  <si>
+    <t>Social phobia, generalized</t>
+  </si>
+  <si>
+    <t>F40.210</t>
+  </si>
+  <si>
+    <t>Arachnophobia</t>
+  </si>
+  <si>
+    <t>F40.218</t>
+  </si>
+  <si>
+    <t>Other animal type phobia</t>
+  </si>
+  <si>
+    <t>F40.220</t>
+  </si>
+  <si>
+    <t>Fear of thunderstorms</t>
+  </si>
+  <si>
+    <t>F40.228</t>
+  </si>
+  <si>
+    <t>Other natural environment type phobia</t>
+  </si>
+  <si>
+    <t>F40.230</t>
+  </si>
+  <si>
+    <t>Fear of blood</t>
+  </si>
+  <si>
+    <t>F40.231</t>
+  </si>
+  <si>
+    <t>Fear of injections and transfusions</t>
+  </si>
+  <si>
+    <t>F40.232</t>
+  </si>
+  <si>
+    <t>Fear of other medical care</t>
+  </si>
+  <si>
+    <t>F40.233</t>
+  </si>
+  <si>
+    <t>Fear of injury</t>
+  </si>
+  <si>
+    <t>F40.240</t>
+  </si>
+  <si>
+    <t>Claustrophobia</t>
+  </si>
+  <si>
+    <t>F40.241</t>
+  </si>
+  <si>
+    <t>Acrophobia</t>
+  </si>
+  <si>
+    <t>F40.242</t>
+  </si>
+  <si>
+    <t>Fear of bridges</t>
+  </si>
+  <si>
+    <t>F40.243</t>
+  </si>
+  <si>
+    <t>Fear of flying</t>
+  </si>
+  <si>
+    <t>F40.248</t>
+  </si>
+  <si>
+    <t>Other situational type phobia</t>
+  </si>
+  <si>
+    <t>F40.290</t>
+  </si>
+  <si>
+    <t>Androphobia</t>
+  </si>
+  <si>
+    <t>F40.291</t>
+  </si>
+  <si>
+    <t>Gynephobia</t>
+  </si>
+  <si>
+    <t>F40.298</t>
+  </si>
+  <si>
+    <t>Other specified phobia</t>
+  </si>
+  <si>
+    <t>F40.8</t>
+  </si>
+  <si>
+    <t>Other phobic anxiety disorders</t>
+  </si>
+  <si>
+    <t>F40.9</t>
+  </si>
+  <si>
+    <t>Phobic anxiety disorder, unspecified</t>
+  </si>
+  <si>
+    <t>F41.0</t>
+  </si>
+  <si>
+    <t>Panic disorder [episodic paroxysmal anxiety]</t>
+  </si>
+  <si>
+    <t>F41.1</t>
+  </si>
+  <si>
+    <t>Generalized anxiety disorder</t>
+  </si>
+  <si>
+    <t>F41.3</t>
+  </si>
+  <si>
+    <t>Other mixed anxiety disorders</t>
+  </si>
+  <si>
+    <t>F41.8</t>
+  </si>
+  <si>
+    <t>Other specified anxiety disorders</t>
+  </si>
+  <si>
+    <t>F41.9</t>
+  </si>
+  <si>
+    <t>Anxiety disorder, unspecified</t>
+  </si>
+  <si>
+    <t>F43.0</t>
+  </si>
+  <si>
+    <t>Acute stress reaction</t>
+  </si>
+  <si>
+    <t>F43.10</t>
+  </si>
+  <si>
+    <t>Post-traumatic stress disorder, unspecified</t>
+  </si>
+  <si>
+    <t>F43.11</t>
+  </si>
+  <si>
+    <t>Post-traumatic stress disorder, acute</t>
+  </si>
+  <si>
+    <t>F43.12</t>
+  </si>
+  <si>
+    <t>Post-traumatic stress disorder, chronic</t>
+  </si>
+  <si>
     <t>F43.20</t>
   </si>
   <si>
@@ -267,70 +483,40 @@
     <t>Adjustment disorder with mixed anxiety and depressed mood</t>
   </si>
   <si>
-    <t>F40.00</t>
-  </si>
-  <si>
-    <t>Agoraphobia, unspecified</t>
-  </si>
-  <si>
-    <t>F40.01</t>
-  </si>
-  <si>
-    <t>Agoraphobia with panic disorder</t>
-  </si>
-  <si>
-    <t>F40.02</t>
-  </si>
-  <si>
-    <t>Agoraphobia without panic disorder</t>
-  </si>
-  <si>
-    <t>F40.10</t>
-  </si>
-  <si>
-    <t>Social phobia, unspecified</t>
-  </si>
-  <si>
-    <t>F40.11</t>
-  </si>
-  <si>
-    <t>Social phobia, generalized</t>
-  </si>
-  <si>
-    <t>F40.9</t>
-  </si>
-  <si>
-    <t>Phobic anxiety disorder, unspecified</t>
-  </si>
-  <si>
-    <t>F41.0</t>
-  </si>
-  <si>
-    <t>Panic disorder [episodic paroxysmal anxiety]</t>
-  </si>
-  <si>
-    <t>F41.1</t>
-  </si>
-  <si>
-    <t>Generalized anxiety disorder</t>
-  </si>
-  <si>
-    <t>F41.3</t>
-  </si>
-  <si>
-    <t>Other mixed anxiety disorders</t>
-  </si>
-  <si>
-    <t>F41.8</t>
-  </si>
-  <si>
-    <t>Other specified anxiety disorders</t>
-  </si>
-  <si>
-    <t>F41.9</t>
-  </si>
-  <si>
-    <t>Anxiety disorder, unspecified</t>
+    <t>F43.24</t>
+  </si>
+  <si>
+    <t>Adjustment disorder with disturbance of conduct</t>
+  </si>
+  <si>
+    <t>F43.25</t>
+  </si>
+  <si>
+    <t>Adjustment disorder with mixed disturbance of emotions and conduct</t>
+  </si>
+  <si>
+    <t>F43.29</t>
+  </si>
+  <si>
+    <t>Adjustment disorder with other symptoms</t>
+  </si>
+  <si>
+    <t>F43.81</t>
+  </si>
+  <si>
+    <t>Prolonged grief disorder</t>
+  </si>
+  <si>
+    <t>F43.89</t>
+  </si>
+  <si>
+    <t>Other reactions to severe stress</t>
+  </si>
+  <si>
+    <t>F43.9</t>
+  </si>
+  <si>
+    <t>Reaction to severe stress, unspecified</t>
   </si>
   <si>
     <t/>
@@ -605,7 +791,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B41"/>
+  <dimension ref="A1:B72"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -929,15 +1115,263 @@
         <v>106</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>170</v>
       </c>
     </row>
   </sheetData>

--- a/ValueSet-ACCESSBHDiagnosisVS.xlsx
+++ b/ValueSet-ACCESSBHDiagnosisVS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-04T22:54:52-04:00</t>
+    <t>2026-06-04T23:05:21-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-ACCESSBHDiagnosisVS.xlsx
+++ b/ValueSet-ACCESSBHDiagnosisVS.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.11</t>
+    <t>0.9.12</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-04T23:05:21-04:00</t>
+    <t>2026-06-10T23:08:55-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
